--- a/artfynd/A 57577-2024 artfynd.xlsx
+++ b/artfynd/A 57577-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137451461</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137451468</v>
       </c>
       <c r="B3" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137451469</v>
       </c>
       <c r="B4" t="n">
-        <v>92104</v>
+        <v>92107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137451470</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137451467</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137451455</v>
       </c>
       <c r="B7" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137451460</v>
       </c>
       <c r="B8" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137451463</v>
       </c>
       <c r="B9" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137451466</v>
       </c>
       <c r="B10" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137451454</v>
       </c>
       <c r="B11" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137451462</v>
       </c>
       <c r="B12" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137451465</v>
       </c>
       <c r="B19" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 57577-2024 artfynd.xlsx
+++ b/artfynd/A 57577-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137451461</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137451468</v>
       </c>
       <c r="B3" t="n">
-        <v>92238</v>
+        <v>92242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137451469</v>
       </c>
       <c r="B4" t="n">
-        <v>92107</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137451470</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137451467</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137451455</v>
       </c>
       <c r="B7" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137451460</v>
       </c>
       <c r="B8" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137451463</v>
       </c>
       <c r="B9" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137451466</v>
       </c>
       <c r="B10" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137451454</v>
       </c>
       <c r="B11" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137451462</v>
       </c>
       <c r="B12" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>137451453</v>
       </c>
       <c r="B13" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137451456</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>137451457</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>137451458</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137451459</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>137451464</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137451465</v>
       </c>
       <c r="B19" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
